--- a/stocks.xlsx
+++ b/stocks.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G424"/>
+  <dimension ref="A1:G501"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9348,6 +9348,1623 @@
       <c r="F424" t="inlineStr"/>
       <c r="G424" t="inlineStr"/>
     </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>PURR</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>Hyperliquid Strategies Inc</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr"/>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr"/>
+      <c r="F425" t="inlineStr"/>
+      <c r="G425" t="inlineStr"/>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>BTBT</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>Bit Digital, Inc.</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr"/>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr"/>
+      <c r="F426" t="inlineStr"/>
+      <c r="G426" t="inlineStr"/>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>MSTR</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>Strategy Inc</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr"/>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr"/>
+      <c r="F427" t="inlineStr"/>
+      <c r="G427" t="inlineStr"/>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>Hecla Mining Company</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr"/>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr"/>
+      <c r="F428" t="inlineStr"/>
+      <c r="G428" t="inlineStr"/>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>NKE</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>Nike, Inc.</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr"/>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr"/>
+      <c r="F429" t="inlineStr"/>
+      <c r="G429" t="inlineStr"/>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>FIG</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>Figma, Inc.</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr"/>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr"/>
+      <c r="F430" t="inlineStr"/>
+      <c r="G430" t="inlineStr"/>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>BULL</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>Webull Corporation</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr"/>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr"/>
+      <c r="F431" t="inlineStr"/>
+      <c r="G431" t="inlineStr"/>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>RKT</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>Rocket Companies, Inc.</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr"/>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr"/>
+      <c r="F432" t="inlineStr"/>
+      <c r="G432" t="inlineStr"/>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>CRWD</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>CrowdStrike Holdings, Inc.</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr"/>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr"/>
+      <c r="F433" t="inlineStr"/>
+      <c r="G433" t="inlineStr"/>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>WEN</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>Wendy's Company (The)</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr"/>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr"/>
+      <c r="F434" t="inlineStr"/>
+      <c r="G434" t="inlineStr"/>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>MRNA</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>Moderna, Inc.</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr"/>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr"/>
+      <c r="F435" t="inlineStr"/>
+      <c r="G435" t="inlineStr"/>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>HBAN</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>Huntington Bancshares Incorpora</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr"/>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr"/>
+      <c r="F436" t="inlineStr"/>
+      <c r="G436" t="inlineStr"/>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>RZLV</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>Rezolve AI PLC</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr"/>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr"/>
+      <c r="F437" t="inlineStr"/>
+      <c r="G437" t="inlineStr"/>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>PBR</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>Petroleo Brasileiro S.A. Petrob</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr"/>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr"/>
+      <c r="F438" t="inlineStr"/>
+      <c r="G438" t="inlineStr"/>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>TWO</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>Two Harbors Investment Corp</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr"/>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr"/>
+      <c r="F439" t="inlineStr"/>
+      <c r="G439" t="inlineStr"/>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>TTD</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>The Trade Desk, Inc.</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr"/>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr"/>
+      <c r="F440" t="inlineStr"/>
+      <c r="G440" t="inlineStr"/>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>FRMI</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>Fermi Inc.</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr"/>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr"/>
+      <c r="F441" t="inlineStr"/>
+      <c r="G441" t="inlineStr"/>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>CCL</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>Carnival Corporation Ltd.</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr"/>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr"/>
+      <c r="F442" t="inlineStr"/>
+      <c r="G442" t="inlineStr"/>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>OKTA</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>Okta, Inc.</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr"/>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr"/>
+      <c r="F443" t="inlineStr"/>
+      <c r="G443" t="inlineStr"/>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>SentinelOne, Inc.</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr"/>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr"/>
+      <c r="F444" t="inlineStr"/>
+      <c r="G444" t="inlineStr"/>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>TOST</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>Toast, Inc.</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr"/>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr"/>
+      <c r="F445" t="inlineStr"/>
+      <c r="G445" t="inlineStr"/>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>SLB</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>SLB Limited</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr"/>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr"/>
+      <c r="F446" t="inlineStr"/>
+      <c r="G446" t="inlineStr"/>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>HPE</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>Hewlett Packard Enterprise Comp</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr"/>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E447" t="inlineStr"/>
+      <c r="F447" t="inlineStr"/>
+      <c r="G447" t="inlineStr"/>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>WIT</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>Wipro Limited</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr"/>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr"/>
+      <c r="F448" t="inlineStr"/>
+      <c r="G448" t="inlineStr"/>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>USAR</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>USA Rare Earth, Inc.</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr"/>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr"/>
+      <c r="F449" t="inlineStr"/>
+      <c r="G449" t="inlineStr"/>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>BABA</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>Alibaba Group Holding Limited</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr"/>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E450" t="inlineStr"/>
+      <c r="F450" t="inlineStr"/>
+      <c r="G450" t="inlineStr"/>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>UBER</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>Uber Technologies, Inc.</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr"/>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E451" t="inlineStr"/>
+      <c r="F451" t="inlineStr"/>
+      <c r="G451" t="inlineStr"/>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>LFU2.F</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>Bakrie &amp; Brothers, PT         R</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr"/>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr"/>
+      <c r="F452" t="inlineStr"/>
+      <c r="G452" t="inlineStr"/>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>CK8.F</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>GoTo Gojek Tokopedia Tbk      R</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr"/>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E453" t="inlineStr"/>
+      <c r="F453" t="inlineStr"/>
+      <c r="G453" t="inlineStr"/>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>VRV.DE</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>Verve Group Media SE          N</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr"/>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E454" t="inlineStr"/>
+      <c r="F454" t="inlineStr"/>
+      <c r="G454" t="inlineStr"/>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>NVD.DE</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>NVIDIA CORP.                  R</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr"/>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E455" t="inlineStr"/>
+      <c r="F455" t="inlineStr"/>
+      <c r="G455" t="inlineStr"/>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>EVD.DE</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>CTS Eventim AG &amp; Co. KGaA     I</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr"/>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr"/>
+      <c r="F456" t="inlineStr"/>
+      <c r="G456" t="inlineStr"/>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>HRT.F</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>SHERRITT INTERNATIONAL CORP.  R</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr"/>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr"/>
+      <c r="F457" t="inlineStr"/>
+      <c r="G457" t="inlineStr"/>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>TNIE.DE</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>tonies SE                     A</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr"/>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr"/>
+      <c r="F458" t="inlineStr"/>
+      <c r="G458" t="inlineStr"/>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>EPU.F</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>Emperor Watch &amp; Jewellery Ltd.R</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr"/>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr"/>
+      <c r="F459" t="inlineStr"/>
+      <c r="G459" t="inlineStr"/>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>B2K.F</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>Bell Equipment Ltd.           R</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr"/>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr"/>
+      <c r="F460" t="inlineStr"/>
+      <c r="G460" t="inlineStr"/>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>GLJ.DE</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>GRENKE AG                     N</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr"/>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr"/>
+      <c r="F461" t="inlineStr"/>
+      <c r="G461" t="inlineStr"/>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>AMV0.DE</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>AUMOVIO SE                    N</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr"/>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr"/>
+      <c r="F462" t="inlineStr"/>
+      <c r="G462" t="inlineStr"/>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>MRK.DE</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>MERCK KGAA                    I</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr"/>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr"/>
+      <c r="F463" t="inlineStr"/>
+      <c r="G463" t="inlineStr"/>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>GFG.DE</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>Global Fashion Group S.A.     B</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr"/>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E464" t="inlineStr"/>
+      <c r="F464" t="inlineStr"/>
+      <c r="G464" t="inlineStr"/>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>GBF.DE</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>Bilfinger SE                  I</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr"/>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E465" t="inlineStr"/>
+      <c r="F465" t="inlineStr"/>
+      <c r="G465" t="inlineStr"/>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>BNR.DE</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>Brenntag SE                   N</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr"/>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E466" t="inlineStr"/>
+      <c r="F466" t="inlineStr"/>
+      <c r="G466" t="inlineStr"/>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>KBX.DE</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>Knorr-Bremse AG               I</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr"/>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E467" t="inlineStr"/>
+      <c r="F467" t="inlineStr"/>
+      <c r="G467" t="inlineStr"/>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>SZG.DE</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>SALZGITTER AG                 I</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr"/>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E468" t="inlineStr"/>
+      <c r="F468" t="inlineStr"/>
+      <c r="G468" t="inlineStr"/>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>NOV.DE</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>Novo-Nordisk AS               N</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr"/>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E469" t="inlineStr"/>
+      <c r="F469" t="inlineStr"/>
+      <c r="G469" t="inlineStr"/>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>TBA.F</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>Bukit Asam (Persero) TBK, PT  R</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr"/>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E470" t="inlineStr"/>
+      <c r="F470" t="inlineStr"/>
+      <c r="G470" t="inlineStr"/>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>LEG.DE</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>LEG Immobilien SE             N</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr"/>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E471" t="inlineStr"/>
+      <c r="F471" t="inlineStr"/>
+      <c r="G471" t="inlineStr"/>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>0147.HK</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>IB SETTLEMENT</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr"/>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="E472" t="inlineStr"/>
+      <c r="F472" t="inlineStr"/>
+      <c r="G472" t="inlineStr"/>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>0460.HK</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>SIHUAN PHARM</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr"/>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="E473" t="inlineStr"/>
+      <c r="F473" t="inlineStr"/>
+      <c r="G473" t="inlineStr"/>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>0371.HK</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>BJ ENT WATER</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr"/>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="E474" t="inlineStr"/>
+      <c r="F474" t="inlineStr"/>
+      <c r="G474" t="inlineStr"/>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>8299.HK</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>GT GOLD</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr"/>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="E475" t="inlineStr"/>
+      <c r="F475" t="inlineStr"/>
+      <c r="G475" t="inlineStr"/>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>6182.HK</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>TWINTEK</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr"/>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="E476" t="inlineStr"/>
+      <c r="F476" t="inlineStr"/>
+      <c r="G476" t="inlineStr"/>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>2268.HK</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>WUXI XDC</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr"/>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="E477" t="inlineStr"/>
+      <c r="F477" t="inlineStr"/>
+      <c r="G477" t="inlineStr"/>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>0189.HK</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>DONGYUE GROUP</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr"/>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="E478" t="inlineStr"/>
+      <c r="F478" t="inlineStr"/>
+      <c r="G478" t="inlineStr"/>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>2319.HK</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>MENGNIU DAIRY</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr"/>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr"/>
+      <c r="F479" t="inlineStr"/>
+      <c r="G479" t="inlineStr"/>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>6186.HK</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>CHINA FEIHE</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr"/>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="E480" t="inlineStr"/>
+      <c r="F480" t="inlineStr"/>
+      <c r="G480" t="inlineStr"/>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>1258.HK</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>CHINFMINING</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr"/>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="E481" t="inlineStr"/>
+      <c r="F481" t="inlineStr"/>
+      <c r="G481" t="inlineStr"/>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>3738.HK</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>VOBILE GROUP</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr"/>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="E482" t="inlineStr"/>
+      <c r="F482" t="inlineStr"/>
+      <c r="G482" t="inlineStr"/>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>6862.HK</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>HAIDILAO</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr"/>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="E483" t="inlineStr"/>
+      <c r="F483" t="inlineStr"/>
+      <c r="G483" t="inlineStr"/>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>0412.HK</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>SDHG</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr"/>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="E484" t="inlineStr"/>
+      <c r="F484" t="inlineStr"/>
+      <c r="G484" t="inlineStr"/>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>2333.HK</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>GWMOTOR</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr"/>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="E485" t="inlineStr"/>
+      <c r="F485" t="inlineStr"/>
+      <c r="G485" t="inlineStr"/>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>2535.HK</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>WK GROUP</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr"/>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="E486" t="inlineStr"/>
+      <c r="F486" t="inlineStr"/>
+      <c r="G486" t="inlineStr"/>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>0340.HK</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>TONGGUAN GOLD</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr"/>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="E487" t="inlineStr"/>
+      <c r="F487" t="inlineStr"/>
+      <c r="G487" t="inlineStr"/>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>3692.HK</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>HANSOH PHARMA</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr"/>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="E488" t="inlineStr"/>
+      <c r="F488" t="inlineStr"/>
+      <c r="G488" t="inlineStr"/>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>0631.HK</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>SANY INT'L</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr"/>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="E489" t="inlineStr"/>
+      <c r="F489" t="inlineStr"/>
+      <c r="G489" t="inlineStr"/>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>1818.HK</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>ZHAOJIN MINING</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr"/>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="E490" t="inlineStr"/>
+      <c r="F490" t="inlineStr"/>
+      <c r="G490" t="inlineStr"/>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>9888.HK</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>BIDU-SW</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr"/>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="E491" t="inlineStr"/>
+      <c r="F491" t="inlineStr"/>
+      <c r="G491" t="inlineStr"/>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>0836.HK</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>CHINA RES POWER</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr"/>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="E492" t="inlineStr"/>
+      <c r="F492" t="inlineStr"/>
+      <c r="G492" t="inlineStr"/>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>0291.HK</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>CHINA RES BEER</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr"/>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="E493" t="inlineStr"/>
+      <c r="F493" t="inlineStr"/>
+      <c r="G493" t="inlineStr"/>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>1530.HK</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>3SBIO</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr"/>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="E494" t="inlineStr"/>
+      <c r="F494" t="inlineStr"/>
+      <c r="G494" t="inlineStr"/>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>6185.HK</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>CANSINOBIO</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr"/>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="E495" t="inlineStr"/>
+      <c r="F495" t="inlineStr"/>
+      <c r="G495" t="inlineStr"/>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>0697.HK</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>SHOUCHENG</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr"/>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="E496" t="inlineStr"/>
+      <c r="F496" t="inlineStr"/>
+      <c r="G496" t="inlineStr"/>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>2382.HK</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>SUNNY OPTICAL</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr"/>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="E497" t="inlineStr"/>
+      <c r="F497" t="inlineStr"/>
+      <c r="G497" t="inlineStr"/>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>3759.HK</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>PHARMARON</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr"/>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="E498" t="inlineStr"/>
+      <c r="F498" t="inlineStr"/>
+      <c r="G498" t="inlineStr"/>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>1585.HK</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>YADEA</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr"/>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="E499" t="inlineStr"/>
+      <c r="F499" t="inlineStr"/>
+      <c r="G499" t="inlineStr"/>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>2157.HK</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>LEPU BIO</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr"/>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="E500" t="inlineStr"/>
+      <c r="F500" t="inlineStr"/>
+      <c r="G500" t="inlineStr"/>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>2028.HK</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>JOLIMARK</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr"/>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="E501" t="inlineStr"/>
+      <c r="F501" t="inlineStr"/>
+      <c r="G501" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
